--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119590931</v>
+        <v>119590958</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455917</v>
+        <v>455857</v>
       </c>
       <c r="R3" t="n">
-        <v>6814121</v>
+        <v>6814027</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119590958</v>
+        <v>119590931</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455857</v>
+        <v>455917</v>
       </c>
       <c r="R4" t="n">
-        <v>6814027</v>
+        <v>6814121</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590956</v>
+        <v>119590929</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590928</v>
+        <v>119590956</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455991</v>
+        <v>455998</v>
       </c>
       <c r="R7" t="n">
-        <v>6813941</v>
+        <v>6813953</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119590929</v>
+        <v>119590928</v>
       </c>
       <c r="B8" t="n">
         <v>79144</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455998</v>
+        <v>455991</v>
       </c>
       <c r="R8" t="n">
-        <v>6813953</v>
+        <v>6813941</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590932</v>
+        <v>119590951</v>
       </c>
       <c r="B31" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455911</v>
+        <v>455998</v>
       </c>
       <c r="R31" t="n">
-        <v>6814102</v>
+        <v>6814113</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590955</v>
+        <v>119590932</v>
       </c>
       <c r="B32" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455983</v>
+        <v>455911</v>
       </c>
       <c r="R32" t="n">
-        <v>6813847</v>
+        <v>6814102</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590951</v>
+        <v>119590955</v>
       </c>
       <c r="B33" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455998</v>
+        <v>455983</v>
       </c>
       <c r="R33" t="n">
-        <v>6814113</v>
+        <v>6813847</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590929</v>
+        <v>119590956</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590956</v>
+        <v>119590929</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119590960</v>
+        <v>119590959</v>
       </c>
       <c r="B2" t="n">
         <v>78526</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455882</v>
+        <v>455919</v>
       </c>
       <c r="R2" t="n">
-        <v>6813847</v>
+        <v>6814002</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119590958</v>
+        <v>119590932</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455857</v>
+        <v>455911</v>
       </c>
       <c r="R3" t="n">
-        <v>6814027</v>
+        <v>6814102</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119590931</v>
+        <v>119590926</v>
       </c>
       <c r="B4" t="n">
         <v>79144</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455917</v>
+        <v>455897</v>
       </c>
       <c r="R4" t="n">
-        <v>6814121</v>
+        <v>6813822</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119590934</v>
+        <v>119590964</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455880</v>
+        <v>455996</v>
       </c>
       <c r="R5" t="n">
-        <v>6813852</v>
+        <v>6813934</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590956</v>
+        <v>119590962</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455998</v>
+        <v>455901</v>
       </c>
       <c r="R6" t="n">
-        <v>6813953</v>
+        <v>6813819</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590929</v>
+        <v>119590938</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455998</v>
+        <v>455983</v>
       </c>
       <c r="R7" t="n">
-        <v>6813953</v>
+        <v>6814010</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119590928</v>
+        <v>119590947</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455991</v>
+        <v>455966</v>
       </c>
       <c r="R8" t="n">
-        <v>6813941</v>
+        <v>6813843</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119590961</v>
+        <v>119590966</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455881</v>
+        <v>455897</v>
       </c>
       <c r="R9" t="n">
-        <v>6813843</v>
+        <v>6813822</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119590948</v>
+        <v>119590931</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455984</v>
+        <v>455917</v>
       </c>
       <c r="R10" t="n">
-        <v>6813847</v>
+        <v>6814121</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119590953</v>
+        <v>119590950</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455754</v>
+        <v>456000</v>
       </c>
       <c r="R11" t="n">
-        <v>6814028</v>
+        <v>6814036</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119590935</v>
+        <v>119590946</v>
       </c>
       <c r="B12" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455984</v>
+        <v>455929</v>
       </c>
       <c r="R12" t="n">
-        <v>6813847</v>
+        <v>6814139</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590926</v>
+        <v>119590958</v>
       </c>
       <c r="B13" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455897</v>
+        <v>455857</v>
       </c>
       <c r="R13" t="n">
-        <v>6813822</v>
+        <v>6814027</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119590940</v>
+        <v>119590951</v>
       </c>
       <c r="B14" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455754</v>
+        <v>455998</v>
       </c>
       <c r="R14" t="n">
-        <v>6814055</v>
+        <v>6814113</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119590949</v>
+        <v>119590929</v>
       </c>
       <c r="B15" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455999</v>
+        <v>455998</v>
       </c>
       <c r="R15" t="n">
         <v>6813953</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119590930</v>
+        <v>119590960</v>
       </c>
       <c r="B16" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456000</v>
+        <v>455882</v>
       </c>
       <c r="R16" t="n">
-        <v>6814036</v>
+        <v>6813847</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119590963</v>
+        <v>119590930</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455926</v>
+        <v>456000</v>
       </c>
       <c r="R17" t="n">
-        <v>6813813</v>
+        <v>6814036</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590947</v>
+        <v>119590949</v>
       </c>
       <c r="B18" t="n">
         <v>78263</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455966</v>
+        <v>455999</v>
       </c>
       <c r="R18" t="n">
-        <v>6813843</v>
+        <v>6813953</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119590952</v>
+        <v>119590961</v>
       </c>
       <c r="B19" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455991</v>
+        <v>455881</v>
       </c>
       <c r="R19" t="n">
-        <v>6813941</v>
+        <v>6813843</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119590939</v>
+        <v>119590956</v>
       </c>
       <c r="B20" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455929</v>
+        <v>455998</v>
       </c>
       <c r="R20" t="n">
-        <v>6814140</v>
+        <v>6813953</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119590964</v>
+        <v>119590939</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455996</v>
+        <v>455929</v>
       </c>
       <c r="R21" t="n">
-        <v>6813934</v>
+        <v>6814140</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119590957</v>
+        <v>119590927</v>
       </c>
       <c r="B22" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455929</v>
+        <v>455934</v>
       </c>
       <c r="R22" t="n">
-        <v>6814139</v>
+        <v>6813963</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119590959</v>
+        <v>119590963</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455919</v>
+        <v>455926</v>
       </c>
       <c r="R23" t="n">
-        <v>6814002</v>
+        <v>6813813</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119590950</v>
+        <v>119590955</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>456000</v>
+        <v>455983</v>
       </c>
       <c r="R24" t="n">
-        <v>6814036</v>
+        <v>6813847</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590938</v>
+        <v>119590928</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455983</v>
+        <v>455991</v>
       </c>
       <c r="R25" t="n">
-        <v>6814010</v>
+        <v>6813941</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119590946</v>
+        <v>119590953</v>
       </c>
       <c r="B26" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455929</v>
+        <v>455754</v>
       </c>
       <c r="R26" t="n">
-        <v>6814139</v>
+        <v>6814028</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119590965</v>
+        <v>119590957</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455876</v>
+        <v>455929</v>
       </c>
       <c r="R27" t="n">
-        <v>6813833</v>
+        <v>6814139</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119590927</v>
+        <v>119590935</v>
       </c>
       <c r="B28" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455934</v>
+        <v>455984</v>
       </c>
       <c r="R28" t="n">
-        <v>6813963</v>
+        <v>6813847</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119590962</v>
+        <v>119590934</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455901</v>
+        <v>455880</v>
       </c>
       <c r="R29" t="n">
-        <v>6813819</v>
+        <v>6813852</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119590966</v>
+        <v>119590952</v>
       </c>
       <c r="B30" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455897</v>
+        <v>455991</v>
       </c>
       <c r="R30" t="n">
-        <v>6813822</v>
+        <v>6813941</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590951</v>
+        <v>119590965</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455998</v>
+        <v>455876</v>
       </c>
       <c r="R31" t="n">
-        <v>6814113</v>
+        <v>6813833</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590932</v>
+        <v>119590940</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455911</v>
+        <v>455754</v>
       </c>
       <c r="R32" t="n">
-        <v>6814102</v>
+        <v>6814055</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590955</v>
+        <v>119590948</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455983</v>
+        <v>455984</v>
       </c>
       <c r="R33" t="n">
         <v>6813847</v>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119590930</v>
+        <v>119590949</v>
       </c>
       <c r="B17" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456000</v>
+        <v>455999</v>
       </c>
       <c r="R17" t="n">
-        <v>6814036</v>
+        <v>6813953</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590949</v>
+        <v>119590930</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455999</v>
+        <v>456000</v>
       </c>
       <c r="R18" t="n">
-        <v>6813953</v>
+        <v>6814036</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119590939</v>
+        <v>119590927</v>
       </c>
       <c r="B21" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455929</v>
+        <v>455934</v>
       </c>
       <c r="R21" t="n">
-        <v>6814140</v>
+        <v>6813963</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119590927</v>
+        <v>119590939</v>
       </c>
       <c r="B22" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455934</v>
+        <v>455929</v>
       </c>
       <c r="R22" t="n">
-        <v>6813963</v>
+        <v>6814140</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119590959</v>
+        <v>119590966</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455919</v>
+        <v>455897</v>
       </c>
       <c r="R2" t="n">
-        <v>6814002</v>
+        <v>6813822</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119590932</v>
+        <v>119590939</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455911</v>
+        <v>455929</v>
       </c>
       <c r="R3" t="n">
-        <v>6814102</v>
+        <v>6814140</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119590926</v>
+        <v>119590963</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455897</v>
+        <v>455926</v>
       </c>
       <c r="R4" t="n">
-        <v>6813822</v>
+        <v>6813813</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119590964</v>
+        <v>119590958</v>
       </c>
       <c r="B5" t="n">
         <v>78526</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455996</v>
+        <v>455857</v>
       </c>
       <c r="R5" t="n">
-        <v>6813934</v>
+        <v>6814027</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590962</v>
+        <v>119590929</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455901</v>
+        <v>455998</v>
       </c>
       <c r="R6" t="n">
-        <v>6813819</v>
+        <v>6813953</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590938</v>
+        <v>119590949</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455983</v>
+        <v>455999</v>
       </c>
       <c r="R7" t="n">
-        <v>6814010</v>
+        <v>6813953</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119590947</v>
+        <v>119590962</v>
       </c>
       <c r="B8" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455966</v>
+        <v>455901</v>
       </c>
       <c r="R8" t="n">
-        <v>6813843</v>
+        <v>6813819</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119590966</v>
+        <v>119590938</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455897</v>
+        <v>455983</v>
       </c>
       <c r="R9" t="n">
-        <v>6813822</v>
+        <v>6814010</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119590931</v>
+        <v>119590964</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455917</v>
+        <v>455996</v>
       </c>
       <c r="R10" t="n">
-        <v>6814121</v>
+        <v>6813934</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119590950</v>
+        <v>119590947</v>
       </c>
       <c r="B11" t="n">
         <v>78263</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456000</v>
+        <v>455966</v>
       </c>
       <c r="R11" t="n">
-        <v>6814036</v>
+        <v>6813843</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119590946</v>
+        <v>119590961</v>
       </c>
       <c r="B12" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455929</v>
+        <v>455881</v>
       </c>
       <c r="R12" t="n">
-        <v>6814139</v>
+        <v>6813843</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590958</v>
+        <v>119590956</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455857</v>
+        <v>455998</v>
       </c>
       <c r="R13" t="n">
-        <v>6814027</v>
+        <v>6813953</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119590951</v>
+        <v>119590960</v>
       </c>
       <c r="B14" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455998</v>
+        <v>455882</v>
       </c>
       <c r="R14" t="n">
-        <v>6814113</v>
+        <v>6813847</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119590929</v>
+        <v>119590928</v>
       </c>
       <c r="B15" t="n">
         <v>79144</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455998</v>
+        <v>455991</v>
       </c>
       <c r="R15" t="n">
-        <v>6813953</v>
+        <v>6813941</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119590960</v>
+        <v>119590953</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455882</v>
+        <v>455754</v>
       </c>
       <c r="R16" t="n">
-        <v>6813847</v>
+        <v>6814028</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119590949</v>
+        <v>119590952</v>
       </c>
       <c r="B17" t="n">
         <v>78263</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455999</v>
+        <v>455991</v>
       </c>
       <c r="R17" t="n">
-        <v>6813953</v>
+        <v>6813941</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590930</v>
+        <v>119590946</v>
       </c>
       <c r="B18" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456000</v>
+        <v>455929</v>
       </c>
       <c r="R18" t="n">
-        <v>6814036</v>
+        <v>6814139</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119590961</v>
+        <v>119590927</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455881</v>
+        <v>455934</v>
       </c>
       <c r="R19" t="n">
-        <v>6813843</v>
+        <v>6813963</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119590956</v>
+        <v>119590959</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455998</v>
+        <v>455919</v>
       </c>
       <c r="R20" t="n">
-        <v>6813953</v>
+        <v>6814002</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119590927</v>
+        <v>119590926</v>
       </c>
       <c r="B21" t="n">
         <v>79144</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455934</v>
+        <v>455897</v>
       </c>
       <c r="R21" t="n">
-        <v>6813963</v>
+        <v>6813822</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119590939</v>
+        <v>119590951</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455929</v>
+        <v>455998</v>
       </c>
       <c r="R22" t="n">
-        <v>6814140</v>
+        <v>6814113</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119590963</v>
+        <v>119590935</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455926</v>
+        <v>455984</v>
       </c>
       <c r="R23" t="n">
-        <v>6813813</v>
+        <v>6813847</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119590955</v>
+        <v>119590948</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455983</v>
+        <v>455984</v>
       </c>
       <c r="R24" t="n">
         <v>6813847</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590928</v>
+        <v>119590965</v>
       </c>
       <c r="B25" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455991</v>
+        <v>455876</v>
       </c>
       <c r="R25" t="n">
-        <v>6813941</v>
+        <v>6813833</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119590953</v>
+        <v>119590931</v>
       </c>
       <c r="B26" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455754</v>
+        <v>455917</v>
       </c>
       <c r="R26" t="n">
-        <v>6814028</v>
+        <v>6814121</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119590935</v>
+        <v>119590932</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455984</v>
+        <v>455911</v>
       </c>
       <c r="R28" t="n">
-        <v>6813847</v>
+        <v>6814102</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119590952</v>
+        <v>119590940</v>
       </c>
       <c r="B30" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455991</v>
+        <v>455754</v>
       </c>
       <c r="R30" t="n">
-        <v>6813941</v>
+        <v>6814055</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590965</v>
+        <v>119590955</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455876</v>
+        <v>455983</v>
       </c>
       <c r="R31" t="n">
-        <v>6813833</v>
+        <v>6813847</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590940</v>
+        <v>119590930</v>
       </c>
       <c r="B32" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455754</v>
+        <v>456000</v>
       </c>
       <c r="R32" t="n">
-        <v>6814055</v>
+        <v>6814036</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590948</v>
+        <v>119590950</v>
       </c>
       <c r="B33" t="n">
         <v>78263</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455984</v>
+        <v>456000</v>
       </c>
       <c r="R33" t="n">
-        <v>6813847</v>
+        <v>6814036</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119590939</v>
+        <v>119590963</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455929</v>
+        <v>455926</v>
       </c>
       <c r="R3" t="n">
-        <v>6814140</v>
+        <v>6813813</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119590963</v>
+        <v>119590939</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455926</v>
+        <v>455929</v>
       </c>
       <c r="R4" t="n">
-        <v>6813813</v>
+        <v>6814140</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119590958</v>
+        <v>119590949</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455857</v>
+        <v>455999</v>
       </c>
       <c r="R5" t="n">
-        <v>6814027</v>
+        <v>6813953</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590929</v>
+        <v>119590958</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455998</v>
+        <v>455857</v>
       </c>
       <c r="R6" t="n">
-        <v>6813953</v>
+        <v>6814027</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590949</v>
+        <v>119590929</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455999</v>
+        <v>455998</v>
       </c>
       <c r="R7" t="n">
         <v>6813953</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590955</v>
+        <v>119590950</v>
       </c>
       <c r="B31" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455983</v>
+        <v>456000</v>
       </c>
       <c r="R31" t="n">
-        <v>6813847</v>
+        <v>6814036</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590930</v>
+        <v>119590955</v>
       </c>
       <c r="B32" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>456000</v>
+        <v>455983</v>
       </c>
       <c r="R32" t="n">
-        <v>6814036</v>
+        <v>6813847</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590950</v>
+        <v>119590930</v>
       </c>
       <c r="B33" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119590966</v>
+        <v>119590928</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455897</v>
+        <v>455991</v>
       </c>
       <c r="R2" t="n">
-        <v>6813822</v>
+        <v>6813941</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119590963</v>
+        <v>119590938</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455926</v>
+        <v>455983</v>
       </c>
       <c r="R3" t="n">
-        <v>6813813</v>
+        <v>6814010</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119590939</v>
+        <v>119590929</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455929</v>
+        <v>455998</v>
       </c>
       <c r="R4" t="n">
-        <v>6814140</v>
+        <v>6813953</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119590949</v>
+        <v>119590926</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455999</v>
+        <v>455897</v>
       </c>
       <c r="R5" t="n">
-        <v>6813953</v>
+        <v>6813822</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590958</v>
+        <v>119590930</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455857</v>
+        <v>456000</v>
       </c>
       <c r="R6" t="n">
-        <v>6814027</v>
+        <v>6814036</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590929</v>
+        <v>119590957</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455998</v>
+        <v>455929</v>
       </c>
       <c r="R7" t="n">
-        <v>6813953</v>
+        <v>6814139</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119590962</v>
+        <v>119590955</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455901</v>
+        <v>455983</v>
       </c>
       <c r="R8" t="n">
-        <v>6813819</v>
+        <v>6813847</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119590938</v>
+        <v>119590946</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455983</v>
+        <v>455929</v>
       </c>
       <c r="R9" t="n">
-        <v>6814010</v>
+        <v>6814139</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119590964</v>
+        <v>119590949</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455996</v>
+        <v>455999</v>
       </c>
       <c r="R10" t="n">
-        <v>6813934</v>
+        <v>6813953</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119590947</v>
+        <v>119590950</v>
       </c>
       <c r="B11" t="n">
         <v>78263</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455966</v>
+        <v>456000</v>
       </c>
       <c r="R11" t="n">
-        <v>6813843</v>
+        <v>6814036</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119590961</v>
+        <v>119590959</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455881</v>
+        <v>455919</v>
       </c>
       <c r="R12" t="n">
-        <v>6813843</v>
+        <v>6814002</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590956</v>
+        <v>119590965</v>
       </c>
       <c r="B13" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455998</v>
+        <v>455876</v>
       </c>
       <c r="R13" t="n">
-        <v>6813953</v>
+        <v>6813833</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119590960</v>
+        <v>119590958</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455882</v>
+        <v>455857</v>
       </c>
       <c r="R14" t="n">
-        <v>6813847</v>
+        <v>6814027</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119590928</v>
+        <v>119590962</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455991</v>
+        <v>455901</v>
       </c>
       <c r="R15" t="n">
-        <v>6813941</v>
+        <v>6813819</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119590953</v>
+        <v>119590966</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455754</v>
+        <v>455897</v>
       </c>
       <c r="R16" t="n">
-        <v>6814028</v>
+        <v>6813822</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119590952</v>
+        <v>119590953</v>
       </c>
       <c r="B17" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455991</v>
+        <v>455754</v>
       </c>
       <c r="R17" t="n">
-        <v>6813941</v>
+        <v>6814028</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590946</v>
+        <v>119590951</v>
       </c>
       <c r="B18" t="n">
         <v>78263</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455929</v>
+        <v>455998</v>
       </c>
       <c r="R18" t="n">
-        <v>6814139</v>
+        <v>6814113</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119590927</v>
+        <v>119590956</v>
       </c>
       <c r="B19" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455934</v>
+        <v>455998</v>
       </c>
       <c r="R19" t="n">
-        <v>6813963</v>
+        <v>6813953</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119590959</v>
+        <v>119590935</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455919</v>
+        <v>455984</v>
       </c>
       <c r="R20" t="n">
-        <v>6814002</v>
+        <v>6813847</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119590926</v>
+        <v>119590963</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455897</v>
+        <v>455926</v>
       </c>
       <c r="R21" t="n">
-        <v>6813822</v>
+        <v>6813813</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119590951</v>
+        <v>119590960</v>
       </c>
       <c r="B22" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455998</v>
+        <v>455882</v>
       </c>
       <c r="R22" t="n">
-        <v>6814113</v>
+        <v>6813847</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119590935</v>
+        <v>119590940</v>
       </c>
       <c r="B23" t="n">
         <v>79115</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455984</v>
+        <v>455754</v>
       </c>
       <c r="R23" t="n">
-        <v>6813847</v>
+        <v>6814055</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119590948</v>
+        <v>119590932</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455984</v>
+        <v>455911</v>
       </c>
       <c r="R24" t="n">
-        <v>6813847</v>
+        <v>6814102</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590965</v>
+        <v>119590939</v>
       </c>
       <c r="B25" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455876</v>
+        <v>455929</v>
       </c>
       <c r="R25" t="n">
-        <v>6813833</v>
+        <v>6814140</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119590931</v>
+        <v>119590934</v>
       </c>
       <c r="B26" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455917</v>
+        <v>455880</v>
       </c>
       <c r="R26" t="n">
-        <v>6814121</v>
+        <v>6813852</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119590957</v>
+        <v>119590948</v>
       </c>
       <c r="B27" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455929</v>
+        <v>455984</v>
       </c>
       <c r="R27" t="n">
-        <v>6814139</v>
+        <v>6813847</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119590932</v>
+        <v>119590961</v>
       </c>
       <c r="B28" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455911</v>
+        <v>455881</v>
       </c>
       <c r="R28" t="n">
-        <v>6814102</v>
+        <v>6813843</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119590934</v>
+        <v>119590931</v>
       </c>
       <c r="B29" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455880</v>
+        <v>455917</v>
       </c>
       <c r="R29" t="n">
-        <v>6813852</v>
+        <v>6814121</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119590940</v>
+        <v>119590947</v>
       </c>
       <c r="B30" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455754</v>
+        <v>455966</v>
       </c>
       <c r="R30" t="n">
-        <v>6814055</v>
+        <v>6813843</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590950</v>
+        <v>119590964</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>456000</v>
+        <v>455996</v>
       </c>
       <c r="R31" t="n">
-        <v>6814036</v>
+        <v>6813934</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590955</v>
+        <v>119590952</v>
       </c>
       <c r="B32" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455983</v>
+        <v>455991</v>
       </c>
       <c r="R32" t="n">
-        <v>6813847</v>
+        <v>6813941</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590930</v>
+        <v>119590927</v>
       </c>
       <c r="B33" t="n">
         <v>79144</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>456000</v>
+        <v>455934</v>
       </c>
       <c r="R33" t="n">
-        <v>6814036</v>
+        <v>6813963</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119590928</v>
+        <v>119590965</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455991</v>
+        <v>455876</v>
       </c>
       <c r="R2" t="n">
-        <v>6813941</v>
+        <v>6813833</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119590938</v>
+        <v>119590966</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455983</v>
+        <v>455897</v>
       </c>
       <c r="R3" t="n">
-        <v>6814010</v>
+        <v>6813822</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119590929</v>
+        <v>119590958</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455998</v>
+        <v>455857</v>
       </c>
       <c r="R4" t="n">
-        <v>6813953</v>
+        <v>6814027</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119590926</v>
+        <v>119590959</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455897</v>
+        <v>455919</v>
       </c>
       <c r="R5" t="n">
-        <v>6813822</v>
+        <v>6814002</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119590930</v>
+        <v>119590960</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456000</v>
+        <v>455882</v>
       </c>
       <c r="R6" t="n">
-        <v>6814036</v>
+        <v>6813847</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119590957</v>
+        <v>119590961</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455929</v>
+        <v>455881</v>
       </c>
       <c r="R7" t="n">
-        <v>6814139</v>
+        <v>6813843</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119590955</v>
+        <v>119590962</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455983</v>
+        <v>455901</v>
       </c>
       <c r="R8" t="n">
-        <v>6813847</v>
+        <v>6813819</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119590946</v>
+        <v>119590963</v>
       </c>
       <c r="B9" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455929</v>
+        <v>455926</v>
       </c>
       <c r="R9" t="n">
-        <v>6814139</v>
+        <v>6813813</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119590949</v>
+        <v>119590964</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455999</v>
+        <v>455996</v>
       </c>
       <c r="R10" t="n">
-        <v>6813953</v>
+        <v>6813934</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119590950</v>
+        <v>119590967</v>
       </c>
       <c r="B11" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456000</v>
+        <v>456026</v>
       </c>
       <c r="R11" t="n">
-        <v>6814036</v>
+        <v>6814093</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119590959</v>
+        <v>119590953</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455919</v>
+        <v>455754</v>
       </c>
       <c r="R12" t="n">
-        <v>6814002</v>
+        <v>6814028</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119590965</v>
+        <v>119590955</v>
       </c>
       <c r="B13" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455876</v>
+        <v>455983</v>
       </c>
       <c r="R13" t="n">
-        <v>6813833</v>
+        <v>6813847</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119590958</v>
+        <v>119590956</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455857</v>
+        <v>455998</v>
       </c>
       <c r="R14" t="n">
-        <v>6814027</v>
+        <v>6813953</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119590962</v>
+        <v>119590957</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455901</v>
+        <v>455929</v>
       </c>
       <c r="R15" t="n">
-        <v>6813819</v>
+        <v>6814139</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119590966</v>
+        <v>119590926</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119590953</v>
+        <v>119590927</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455754</v>
+        <v>455934</v>
       </c>
       <c r="R17" t="n">
-        <v>6814028</v>
+        <v>6813963</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119590951</v>
+        <v>119590928</v>
       </c>
       <c r="B18" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455998</v>
+        <v>455991</v>
       </c>
       <c r="R18" t="n">
-        <v>6814113</v>
+        <v>6813941</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119590956</v>
+        <v>119590929</v>
       </c>
       <c r="B19" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2511,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119590935</v>
+        <v>119590930</v>
       </c>
       <c r="B20" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455984</v>
+        <v>456000</v>
       </c>
       <c r="R20" t="n">
-        <v>6813847</v>
+        <v>6814036</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119590963</v>
+        <v>119590931</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455926</v>
+        <v>455917</v>
       </c>
       <c r="R21" t="n">
-        <v>6813813</v>
+        <v>6814121</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119590960</v>
+        <v>119590932</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455882</v>
+        <v>455911</v>
       </c>
       <c r="R22" t="n">
-        <v>6813847</v>
+        <v>6814102</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2817,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119590940</v>
+        <v>119590933</v>
       </c>
       <c r="B23" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455754</v>
+        <v>455804</v>
       </c>
       <c r="R23" t="n">
-        <v>6814055</v>
+        <v>6814043</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2919,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119590932</v>
+        <v>119590946</v>
       </c>
       <c r="B24" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455911</v>
+        <v>455929</v>
       </c>
       <c r="R24" t="n">
-        <v>6814102</v>
+        <v>6814139</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119590939</v>
+        <v>119590947</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455929</v>
+        <v>455966</v>
       </c>
       <c r="R25" t="n">
-        <v>6814140</v>
+        <v>6813843</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3123,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119590934</v>
+        <v>119590948</v>
       </c>
       <c r="B26" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455880</v>
+        <v>455984</v>
       </c>
       <c r="R26" t="n">
-        <v>6813852</v>
+        <v>6813847</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3225,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119590948</v>
+        <v>119590949</v>
       </c>
       <c r="B27" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455984</v>
+        <v>455999</v>
       </c>
       <c r="R27" t="n">
-        <v>6813847</v>
+        <v>6813953</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3327,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119590961</v>
+        <v>119590950</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455881</v>
+        <v>456000</v>
       </c>
       <c r="R28" t="n">
-        <v>6813843</v>
+        <v>6814036</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3429,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119590931</v>
+        <v>119590951</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3445,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455917</v>
+        <v>455998</v>
       </c>
       <c r="R29" t="n">
-        <v>6814121</v>
+        <v>6814113</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3531,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119590947</v>
+        <v>119590952</v>
       </c>
       <c r="B30" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455966</v>
+        <v>455991</v>
       </c>
       <c r="R30" t="n">
-        <v>6813843</v>
+        <v>6813941</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3633,15 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119590964</v>
+        <v>119590934</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3649,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455996</v>
+        <v>455880</v>
       </c>
       <c r="R31" t="n">
-        <v>6813934</v>
+        <v>6813852</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3735,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119590952</v>
+        <v>119590935</v>
       </c>
       <c r="B32" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455991</v>
+        <v>455984</v>
       </c>
       <c r="R32" t="n">
-        <v>6813941</v>
+        <v>6813847</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3837,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119590927</v>
+        <v>119590936</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455934</v>
+        <v>456001</v>
       </c>
       <c r="R33" t="n">
-        <v>6813963</v>
+        <v>6813969</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3936,6 +3776,297 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>119590938</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kölkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>455983</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6814010</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119590939</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kölkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>455929</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6814140</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>119590940</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kölkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>455754</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6814055</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34447-2024 artfynd.xlsx
+++ b/artfynd/A 34447-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590966</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590959</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590960</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590961</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590962</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590963</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590964</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590967</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590953</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590955</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590956</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590957</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590926</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590927</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590928</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590929</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590930</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590931</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590932</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590933</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590946</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590947</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590948</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590949</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590950</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590951</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590952</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590934</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590935</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590936</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590938</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590939</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,8 +4242,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119590940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>